--- a/stufe-5/terminplanung/migrate-ig-toig-publisher-PTDATA-1943/ValueSet-ISiKValueSetExample.xlsx
+++ b/stufe-5/terminplanung/migrate-ig-toig-publisher-PTDATA-1943/ValueSet-ISiKValueSetExample.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-02T15:42:33+00:00</t>
+    <t>2025-12-04T18:17:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/terminplanung/migrate-ig-toig-publisher-PTDATA-1943/ValueSet-ISiKValueSetExample.xlsx
+++ b/stufe-5/terminplanung/migrate-ig-toig-publisher-PTDATA-1943/ValueSet-ISiKValueSetExample.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-04T18:17:34+00:00</t>
+    <t>2025-12-04T18:40:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/terminplanung/migrate-ig-toig-publisher-PTDATA-1943/ValueSet-ISiKValueSetExample.xlsx
+++ b/stufe-5/terminplanung/migrate-ig-toig-publisher-PTDATA-1943/ValueSet-ISiKValueSetExample.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-04T18:40:53+00:00</t>
+    <t>2025-12-05T07:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/terminplanung/migrate-ig-toig-publisher-PTDATA-1943/ValueSet-ISiKValueSetExample.xlsx
+++ b/stufe-5/terminplanung/migrate-ig-toig-publisher-PTDATA-1943/ValueSet-ISiKValueSetExample.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-05T07:01:43+00:00</t>
+    <t>2025-12-05T07:04:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
